--- a/data/trans_orig/P57_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133560</t>
+          <t>133459</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174202</t>
+          <t>174273</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93734</t>
+          <t>92607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131380</t>
+          <t>128622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239465</t>
+          <t>237153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>297863</t>
+          <t>291541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252938</t>
+          <t>252867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293580</t>
+          <t>293681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>213686</t>
+          <t>216444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251332</t>
+          <t>252459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>474343</t>
+          <t>480665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532741</t>
+          <t>535053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102093</t>
+          <t>100770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137798</t>
+          <t>138815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75034</t>
+          <t>75835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109648</t>
+          <t>108618</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188331</t>
+          <t>189084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>239108</t>
+          <t>238530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>236983</t>
+          <t>235966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>272688</t>
+          <t>274011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>259349</t>
+          <t>260379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293963</t>
+          <t>293162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>504670</t>
+          <t>505248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555447</t>
+          <t>554694</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130248</t>
+          <t>131366</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172423</t>
+          <t>173678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>29930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51563</t>
+          <t>53741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168499</t>
+          <t>168700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219085</t>
+          <t>216257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>346556</t>
+          <t>345301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>388731</t>
+          <t>387613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113015</t>
+          <t>110837</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134285</t>
+          <t>134648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464473</t>
+          <t>467301</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>515059</t>
+          <t>514858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,32%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>291591</t>
+          <t>288818</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>351235</t>
+          <t>348804</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224141</t>
+          <t>222188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276312</t>
+          <t>277359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>526433</t>
+          <t>530084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>609757</t>
+          <t>609753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>794241</t>
+          <t>796672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>853885</t>
+          <t>856658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>548538</t>
+          <t>547491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>600709</t>
+          <t>602662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1360569</t>
+          <t>1360573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1443893</t>
+          <t>1440242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129381</t>
+          <t>128399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173374</t>
+          <t>170378</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115222</t>
+          <t>117031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>156935</t>
+          <t>159929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>253507</t>
+          <t>257088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318030</t>
+          <t>317389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>445209</t>
+          <t>448205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>489202</t>
+          <t>490184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>579098</t>
+          <t>576104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>619002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1036587</t>
+          <t>1037228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1101110</t>
+          <t>1097529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110809</t>
+          <t>111424</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145406</t>
+          <t>146461</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>270209</t>
+          <t>270810</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>329449</t>
+          <t>331291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>393617</t>
+          <t>391921</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>465779</t>
+          <t>463019</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>141739</t>
+          <t>140684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176336</t>
+          <t>175721</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>746184</t>
+          <t>744342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>805424</t>
+          <t>804823</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>896999</t>
+          <t>899759</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>969161</t>
+          <t>970857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,24%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>968191</t>
+          <t>968349</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1077407</t>
+          <t>1083050</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>873031</t>
+          <t>876141</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>983770</t>
+          <t>982442</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1873943</t>
+          <t>1866206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2029429</t>
+          <t>2024809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2294698</t>
+          <t>2289055</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2403914</t>
+          <t>2403756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2531387</t>
+          <t>2532715</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2642126</t>
+          <t>2639016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4857833</t>
+          <t>4862453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5013319</t>
+          <t>5021056</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>195119</t>
+          <t>196268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>242631</t>
+          <t>242682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>194244</t>
+          <t>195413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>231982</t>
+          <t>229644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>405381</t>
+          <t>404433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>462646</t>
+          <t>463136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262581</t>
+          <t>262530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310093</t>
+          <t>308944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>214432</t>
+          <t>216770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252170</t>
+          <t>251001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>488981</t>
+          <t>488491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>546246</t>
+          <t>547194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194001</t>
+          <t>193743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>238279</t>
+          <t>237455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155540</t>
+          <t>153548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>188031</t>
+          <t>185983</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>354845</t>
+          <t>353464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>413529</t>
+          <t>411510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213313</t>
+          <t>214137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257591</t>
+          <t>257849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192951</t>
+          <t>194999</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>225442</t>
+          <t>227434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>419045</t>
+          <t>421064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>477729</t>
+          <t>479110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>314929</t>
+          <t>315026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>584634</t>
+          <t>579750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>55232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>76356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374588</t>
+          <t>376534</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>695780</t>
+          <t>685981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83630</t>
+          <t>88514</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>353335</t>
+          <t>353238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90933</t>
+          <t>90555</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111595</t>
+          <t>111679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139395</t>
+          <t>149194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>460587</t>
+          <t>458641</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>429999</t>
+          <t>430582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>501778</t>
+          <t>505022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178210</t>
+          <t>185711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>429764</t>
+          <t>430545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>529458</t>
+          <t>553632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>901746</t>
+          <t>910388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>527331</t>
+          <t>524087</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>599110</t>
+          <t>598527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>544403</t>
+          <t>543622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>795957</t>
+          <t>788456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1101530</t>
+          <t>1092888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1473818</t>
+          <t>1449644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>184706</t>
+          <t>183731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>231462</t>
+          <t>230361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181994</t>
+          <t>191802</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>286717</t>
+          <t>288405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>370842</t>
+          <t>380577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>501065</t>
+          <t>506285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>241119</t>
+          <t>242220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287875</t>
+          <t>288850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>550490</t>
+          <t>548802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>655213</t>
+          <t>645405</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>808723</t>
+          <t>803503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>938946</t>
+          <t>929211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126498</t>
+          <t>126990</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>176076</t>
+          <t>175767</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>289069</t>
+          <t>288407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>340614</t>
+          <t>343741</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>432117</t>
+          <t>431859</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>504676</t>
+          <t>502864</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64431</t>
+          <t>64740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>113517</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>411824</t>
+          <t>408697</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>463369</t>
+          <t>464031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488269</t>
+          <t>490081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560828</t>
+          <t>561086</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,51%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1562904</t>
+          <t>1568126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2096252</t>
+          <t>2135401</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1102895</t>
+          <t>1081371</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1459442</t>
+          <t>1460668</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2813837</t>
+          <t>2789786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3494405</t>
+          <t>3498025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1271014</t>
+          <t>1231865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1804362</t>
+          <t>1799140</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2098676</t>
+          <t>2097450</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2455223</t>
+          <t>2476747</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3430979</t>
+          <t>3427359</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4111547</t>
+          <t>4135598</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57_R2-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133459</t>
+          <t>134690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174273</t>
+          <t>173795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92607</t>
+          <t>93260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>128678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237153</t>
+          <t>237846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291541</t>
+          <t>291667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252867</t>
+          <t>253345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293681</t>
+          <t>292450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216444</t>
+          <t>216388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252459</t>
+          <t>251806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>480665</t>
+          <t>480539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>535053</t>
+          <t>534360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100770</t>
+          <t>101965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138815</t>
+          <t>140147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75835</t>
+          <t>76140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108618</t>
+          <t>111235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>189084</t>
+          <t>188227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238530</t>
+          <t>237975</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>235966</t>
+          <t>234634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>274011</t>
+          <t>272816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>260379</t>
+          <t>257762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293162</t>
+          <t>292857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>505248</t>
+          <t>505803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>554694</t>
+          <t>555551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131366</t>
+          <t>132834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173678</t>
+          <t>174082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29930</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53741</t>
+          <t>52447</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168700</t>
+          <t>168718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216257</t>
+          <t>218022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>345301</t>
+          <t>344897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>387613</t>
+          <t>386145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110837</t>
+          <t>112131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134648</t>
+          <t>135681</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>467301</t>
+          <t>465536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>514858</t>
+          <t>514840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>288818</t>
+          <t>289822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>348804</t>
+          <t>350030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222188</t>
+          <t>222855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277359</t>
+          <t>274685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>530084</t>
+          <t>531505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>609753</t>
+          <t>609592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>796672</t>
+          <t>795446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>856658</t>
+          <t>855654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>547491</t>
+          <t>550165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>602662</t>
+          <t>601995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1360573</t>
+          <t>1360734</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1440242</t>
+          <t>1438821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,02%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>128399</t>
+          <t>129130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170378</t>
+          <t>172201</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117031</t>
+          <t>114464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159929</t>
+          <t>155329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257088</t>
+          <t>254792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317389</t>
+          <t>316180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448205</t>
+          <t>446382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>490184</t>
+          <t>489453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>576104</t>
+          <t>580704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>619002</t>
+          <t>621569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1037228</t>
+          <t>1038437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1097529</t>
+          <t>1099825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111424</t>
+          <t>112505</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146461</t>
+          <t>146696</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>270810</t>
+          <t>270727</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>331291</t>
+          <t>330785</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>391921</t>
+          <t>392540</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>463019</t>
+          <t>461126</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140684</t>
+          <t>140449</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175721</t>
+          <t>174640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>744342</t>
+          <t>744848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>804823</t>
+          <t>804906</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>899759</t>
+          <t>901652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>970857</t>
+          <t>970238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>968349</t>
+          <t>973646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1083050</t>
+          <t>1084521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>876141</t>
+          <t>876332</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>982442</t>
+          <t>982711</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1866206</t>
+          <t>1880431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2024809</t>
+          <t>2028672</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2289055</t>
+          <t>2287584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2403756</t>
+          <t>2398459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2532715</t>
+          <t>2532446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2639016</t>
+          <t>2638825</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4862453</t>
+          <t>4858590</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5021056</t>
+          <t>5006831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -3361,102 +3361,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>220224</t>
+          <t>241597</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>196268</t>
+          <t>216796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>242682</t>
+          <t>266884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>48,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>227331</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>207972</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>246182</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>46,65%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>42,68%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>50,52%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>468928</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>435681</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>498555</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>45,18%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>41,98%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>48,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>213263</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>195413</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>229644</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,77%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>43,77%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>433487</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>404433</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>463136</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>42,5%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -3474,102 +3474,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>284988</t>
+          <t>309021</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262530</t>
+          <t>283734</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308944</t>
+          <t>333822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>51,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>259948</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>241097</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>279307</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>53,35%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>49,48%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>57,32%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>568969</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>539342</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>602216</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>54,82%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>51,96%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>233151</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>216770</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>251001</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>52,23%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>518140</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>488491</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>547194</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>51,33%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446414</t>
+          <t>487279</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446414</t>
+          <t>487279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446414</t>
+          <t>487279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951627</t>
+          <t>1037897</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951627</t>
+          <t>1037897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951627</t>
+          <t>1037897</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>214912</t>
+          <t>232567</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>193743</t>
+          <t>208713</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237455</t>
+          <t>256946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>170810</t>
+          <t>189044</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153548</t>
+          <t>169538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185983</t>
+          <t>205265</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>385722</t>
+          <t>421611</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>353464</t>
+          <t>394755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>411510</t>
+          <t>451176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>236680</t>
+          <t>249978</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214137</t>
+          <t>225599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257849</t>
+          <t>273832</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>210172</t>
+          <t>232425</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194999</t>
+          <t>216204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>227434</t>
+          <t>251931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>446852</t>
+          <t>482403</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>421064</t>
+          <t>452838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>479110</t>
+          <t>509259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451592</t>
+          <t>482545</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451592</t>
+          <t>482545</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451592</t>
+          <t>482545</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>380982</t>
+          <t>421469</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>380982</t>
+          <t>421469</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380982</t>
+          <t>421469</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>832574</t>
+          <t>904014</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>832574</t>
+          <t>904014</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>832574</t>
+          <t>904014</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>450593</t>
+          <t>226347</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>315026</t>
+          <t>205155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>579750</t>
+          <t>247562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64755</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>62942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>85883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>515348</t>
+          <t>300163</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376534</t>
+          <t>273928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>685981</t>
+          <t>326395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>49,52%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>217671</t>
+          <t>245265</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88514</t>
+          <t>224050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>353238</t>
+          <t>266457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102156</t>
+          <t>113680</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90555</t>
+          <t>101614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111679</t>
+          <t>124555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>319827</t>
+          <t>358946</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>149194</t>
+          <t>332714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>458641</t>
+          <t>385181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>465969</t>
+          <t>506943</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>430582</t>
+          <t>469642</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>505022</t>
+          <t>544119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>331843</t>
+          <t>368335</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185711</t>
+          <t>343745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>430545</t>
+          <t>393524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>797812</t>
+          <t>875279</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>553632</t>
+          <t>832067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>910388</t>
+          <t>924095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>563140</t>
+          <t>618578</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>524087</t>
+          <t>581402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>598527</t>
+          <t>655879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>642324</t>
+          <t>488311</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>543622</t>
+          <t>463122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>788456</t>
+          <t>512901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1205464</t>
+          <t>1106888</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1092888</t>
+          <t>1058072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1449644</t>
+          <t>1150100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1029109</t>
+          <t>1125521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1029109</t>
+          <t>1125521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1029109</t>
+          <t>1125521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>974167</t>
+          <t>856646</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>974167</t>
+          <t>856646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>974167</t>
+          <t>856646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2003276</t>
+          <t>1982167</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2003276</t>
+          <t>1982167</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2003276</t>
+          <t>1982167</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>206441</t>
+          <t>236328</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>183731</t>
+          <t>209852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230361</t>
+          <t>261266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>250189</t>
+          <t>273680</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191802</t>
+          <t>253727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288405</t>
+          <t>298834</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>456630</t>
+          <t>510008</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380577</t>
+          <t>475848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>506285</t>
+          <t>542264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>266140</t>
+          <t>329063</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242220</t>
+          <t>304125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>288850</t>
+          <t>355539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>587018</t>
+          <t>552821</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>548802</t>
+          <t>527667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>645405</t>
+          <t>572774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>853158</t>
+          <t>881883</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>803503</t>
+          <t>849627</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>929211</t>
+          <t>916043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472581</t>
+          <t>565391</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472581</t>
+          <t>565391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472581</t>
+          <t>565391</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837207</t>
+          <t>826501</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837207</t>
+          <t>826501</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837207</t>
+          <t>826501</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1309788</t>
+          <t>1391891</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1309788</t>
+          <t>1391891</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1309788</t>
+          <t>1391891</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>153763</t>
+          <t>150265</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126990</t>
+          <t>124429</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175767</t>
+          <t>170943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>314735</t>
+          <t>353794</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>288407</t>
+          <t>328350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>343741</t>
+          <t>384559</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>468499</t>
+          <t>504059</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>431859</t>
+          <t>466154</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>502864</t>
+          <t>538663</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,2%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>86744</t>
+          <t>86963</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64740</t>
+          <t>66285</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>113517</t>
+          <t>112799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>437703</t>
+          <t>482103</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>408697</t>
+          <t>451338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>464031</t>
+          <t>507547</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>524446</t>
+          <t>569066</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490081</t>
+          <t>534462</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>561086</t>
+          <t>606971</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>752438</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>752438</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>752438</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>992945</t>
+          <t>1073125</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>992945</t>
+          <t>1073125</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>992945</t>
+          <t>1073125</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1711902</t>
+          <t>1594045</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1568126</t>
+          <t>1522212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2135401</t>
+          <t>1656190</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1345595</t>
+          <t>1486001</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1081371</t>
+          <t>1436245</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1460668</t>
+          <t>1540784</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3057497</t>
+          <t>3080047</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2789786</t>
+          <t>2992156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3498025</t>
+          <t>3161226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1655364</t>
+          <t>1838869</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1231865</t>
+          <t>1776724</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1799140</t>
+          <t>1910702</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2212523</t>
+          <t>2129287</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2097450</t>
+          <t>2074504</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2476747</t>
+          <t>2179043</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3867887</t>
+          <t>3968156</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3427359</t>
+          <t>3886977</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4135598</t>
+          <t>4056047</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>57,55%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3367266</t>
+          <t>3432914</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3367266</t>
+          <t>3432914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3367266</t>
+          <t>3432914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3558118</t>
+          <t>3615288</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3558118</t>
+          <t>3615288</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3558118</t>
+          <t>3615288</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6925384</t>
+          <t>7048203</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6925384</t>
+          <t>7048203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6925384</t>
+          <t>7048203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
